--- a/data/trans_bre/IP19C09-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 19,61</t>
+          <t>-3,81; 17,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 0,0</t>
+          <t>-11,41; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 0,0</t>
+          <t>-15,35; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 3,36</t>
+          <t>-2,02; 3,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,4</t>
+          <t>-2,28; 7,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,84</t>
+          <t>1,28; 10,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,53; -1,71</t>
+          <t>-13,89; -1,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 8,97</t>
+          <t>-5,82; 8,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 7,4</t>
+          <t>-4,73; 7,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 0,0</t>
+          <t>-12,46; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 8,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 9,68</t>
+          <t>-8,63; 10,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,23</t>
+          <t>0,0; 18,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 0,0</t>
+          <t>-18,41; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,43</t>
+          <t>0,0; 24,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 9,27</t>
+          <t>-4,68; 10,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,77</t>
+          <t>0,0; 8,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 2,83</t>
+          <t>-10,44; 2,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,6</t>
+          <t>-4,73; 2,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 5,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1194,22 +1194,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,56; -2,17</t>
+          <t>-12,46; -2,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 1,4</t>
+          <t>-7,04; 1,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 3,24</t>
+          <t>-5,7; 2,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -1,85</t>
+          <t>-100,0; 4,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 297,6</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,02</t>
+          <t>-3,46; 0,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,45</t>
+          <t>-1,89; 1,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,12</t>
+          <t>-1,87; 2,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-83,86; 9,42</t>
+          <t>-82,53; 23,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 181,96</t>
+          <t>-71,67; 146,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-58,11; 132,93</t>
+          <t>-55,8; 140,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Provincia-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 17,88</t>
+          <t>-2,42; 17,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 0,0</t>
+          <t>-17,17; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 0,0</t>
+          <t>-14,53; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,35</t>
+          <t>-2,03; 3,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 7,55</t>
+          <t>-2,33; 6,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,72</t>
+          <t>1,27; 11,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,89; -1,72</t>
+          <t>-13,88; -1,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 8,87</t>
+          <t>-5,9; 8,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 7,23</t>
+          <t>-4,76; 7,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 0,0</t>
+          <t>-9,67; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,75</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 10,93</t>
+          <t>-7,2; 9,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,76</t>
+          <t>0,0; 17,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 0,0</t>
+          <t>-16,74; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,96</t>
+          <t>0,0; 22,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 10,88</t>
+          <t>-4,69; 8,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,6</t>
+          <t>0,0; 8,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 2,73</t>
+          <t>-12,04; 3,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 2,43</t>
+          <t>-4,57; 2,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,24</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1194,22 +1194,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,46; -2,14</t>
+          <t>-11,91; -2,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 1,24</t>
+          <t>-7,18; 1,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 2,79</t>
+          <t>-5,57; 2,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 4,9</t>
+          <t>-100,0; -9,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 297,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,11</t>
+          <t>-3,56; 0,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,44</t>
+          <t>-1,91; 1,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,01</t>
+          <t>-1,69; 2,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-82,53; 23,01</t>
+          <t>-85,52; 16,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-71,67; 146,77</t>
+          <t>-70,99; 159,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 140,39</t>
+          <t>-54,12; 165,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Provincia-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 17,48</t>
+          <t>-2,43; 19,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 0,0</t>
+          <t>-13,9; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 0,0</t>
+          <t>-13,64; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,34</t>
+          <t>-2,97; 3,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 6,02</t>
+          <t>-2,32; 6,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,49</t>
+          <t>1,26; 10,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,88; -1,71</t>
+          <t>-15,53; -1,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 8,85</t>
+          <t>-6,23; 8,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 7,49</t>
+          <t>-4,76; 7,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 0,0</t>
+          <t>-10,49; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,38</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 9,69</t>
+          <t>-7,2; 9,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,88</t>
+          <t>0,0; 14,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 0,0</t>
+          <t>-18,76; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,33</t>
+          <t>0,0; 21,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 8,93</t>
+          <t>-4,65; 9,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,64</t>
+          <t>0,0; 12,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 3,0</t>
+          <t>-10,36; 2,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 2,42</t>
+          <t>-3,82; 2,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1194,22 +1194,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,91; -2,21</t>
+          <t>-12,56; -2,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 1,35</t>
+          <t>-7,58; 1,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 2,83</t>
+          <t>-5,16; 3,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,85</t>
+          <t>-100,0; -1,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,19</t>
+          <t>-3,62; 0,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,53</t>
+          <t>-1,81; 1,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,15</t>
+          <t>-1,86; 2,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-85,52; 16,02</t>
+          <t>-83,86; 9,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-70,99; 159,07</t>
+          <t>-69,87; 181,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 165,96</t>
+          <t>-58,11; 132,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Provincia-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,141 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,06</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,83</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>168,75%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.063746922200699</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.829770537294066</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-4.254284238877378</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1.687488266033388</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,43; 19,61</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-13,9; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-13,64; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.434668529702507</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-13.89913093063593</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-13.63630390154057</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>19.61266524231495</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,4</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>64,42%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,97; 3,36</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,32; 6,4</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,26; 10,84</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C7" s="5" t="n">
+        <v>0.106959172728424</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.7385739664693247</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>4.40032960838888</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.1071928140600407</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.6441913675502016</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,19</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>62,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.970828789612106</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.324248934218924</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.264740486545186</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-15,53; -1,71</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,23; 8,97</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,76; 7,4</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.355214983216738</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.396025066581339</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>10.83782709509126</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +745,141 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,97</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.187051034377204</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.700860466132888</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.04458868308678671</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.6290810388776946</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.01904850842787426</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-10,49; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,34</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,2; 9,68</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-15.52902923548139</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.226620524243058</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.760337287470677</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-1.714531304748236</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.974084490175244</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.397251240169019</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,55</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-5,33</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,23</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-18,76; 0,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 21,43</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-1.968410601787593</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.510321403447283</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5088599784470114</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.09801180001759557</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-2,42</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>24,19%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-59,61%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-10.48706344025431</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.199458387250555</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-4,65; 9,27</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,77</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-10,36; 2,83</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.338318713184348</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.68084479922001</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,34 +887,26 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-40,91%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
+      <c r="C16" s="5" t="n">
+        <v>3.54617332885442</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-5.326946166459379</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.126080751930518</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -1109,202 +914,338 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-3,82; 2,6</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,25</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-18.7633948020338</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>14.23430293236086</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>21.42913144810933</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-6,23</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-89,15%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-58,74%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-25,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-12,56; -2,17</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-7,58; 1,4</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-5,16; 3,24</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -1,85</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>0.5625189032632372</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2.10840686598371</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-2.423054264341565</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.2419003049495528</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.5961227201757866</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-54,52%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-10,63%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-4.653501881569947</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-10.35857211980563</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>-3,62; 0,02</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 1,45</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-1,86; 2,12</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>-83,86; 9,42</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-69,87; 181,96</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-58,11; 132,93</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>9.272044367914432</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>12.7660870481909</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2.832236530361333</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.7774271727695903</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1.040324059383153</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-0.4090645498143144</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-3.818286114916308</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2.595349726954629</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>5.250682602668578</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-6.227296711080962</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-2.234889390649011</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-0.8705424737560425</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.8914755480942251</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.5874004326528612</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.2599311201371096</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-12.55743712041885</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-7.575578989943018</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-5.162007834372683</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-2.172353881922795</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1.39628395071444</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>3.243721127070128</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0.01854907449770984</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-1.671419679464448</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.1938696565544074</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.1283082115822249</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-0.545203008732238</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-0.1062768404491198</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0.05305336910917367</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-3.617815544654816</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-1.808478617752896</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-1.858607911069198</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-0.8385625379426065</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-0.6986507045858715</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>-0.5810627472797583</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.01866911455452469</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1.446720939344781</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>2.122949803087668</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.09421649981187356</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>1.819562085037443</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>1.32929966705838</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1313,17 +1254,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
